--- a/artfynd/A 16190-2025 artfynd.xlsx
+++ b/artfynd/A 16190-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126531624</v>
+        <v>126531627</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759173</v>
+        <v>759116</v>
       </c>
       <c r="R3" t="n">
-        <v>7202057</v>
+        <v>7202188</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126531627</v>
+        <v>126531624</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759116</v>
+        <v>759173</v>
       </c>
       <c r="R4" t="n">
-        <v>7202188</v>
+        <v>7202057</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126531573</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126531556</v>
       </c>
       <c r="B7" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>126531625</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126531629</v>
       </c>
       <c r="B14" t="n">
-        <v>80118</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126531615</v>
+        <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>91263</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1974,7 +1974,7 @@
         <v>759153</v>
       </c>
       <c r="R15" t="n">
-        <v>7202048</v>
+        <v>7202046</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126531604</v>
+        <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>91337</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2071,7 +2071,7 @@
         <v>759153</v>
       </c>
       <c r="R16" t="n">
-        <v>7202046</v>
+        <v>7202048</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126531518</v>
+        <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91245</v>
+        <v>91337</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759158</v>
+        <v>759109</v>
       </c>
       <c r="R17" t="n">
-        <v>7202231</v>
+        <v>7202131</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126531616</v>
+        <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>91263</v>
+        <v>98457</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759109</v>
+        <v>759234</v>
       </c>
       <c r="R18" t="n">
-        <v>7202131</v>
+        <v>7201983</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126531542</v>
+        <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>98382</v>
+        <v>91319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759234</v>
+        <v>759158</v>
       </c>
       <c r="R19" t="n">
-        <v>7201983</v>
+        <v>7202231</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
